--- a/resources/fabao.xlsx
+++ b/resources/fabao.xlsx
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>TEST</t>
+          <t>测试描述修改</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">

--- a/resources/fabao.xlsx
+++ b/resources/fabao.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fabao" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="FabaoUpgradeCost" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FabaoLevel" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FabaoSlotUnlockCost" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FabaoType" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="FabaoQuality" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fabao" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FabaoUpgradeCost" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FabaoLevel" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FabaoSlotUnlockCost" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FabaoType" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FabaoQuality" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">Fabao!#REF!</definedName>
@@ -867,7 +867,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -941,6 +941,16 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="9">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -1877,7 +1887,7 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" s="8">
       <c r="A7" s="16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -1949,7 +1959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -2007,7 +2017,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>15004,1</t>
+          <t>10070,5</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
@@ -2103,7 +2113,12 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="8"/>
+    <row r="14" ht="16.5" customHeight="1" s="8">
+      <c r="A14" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="11" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A15:A1048576">
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
@@ -2119,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.5" customWidth="1" style="9" min="1" max="2"/>
@@ -2172,330 +2187,344 @@
       </c>
     </row>
     <row r="3" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>key:1</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>key:1</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
+      <c r="A3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="n">
+        <v>100001</v>
+      </c>
+      <c r="D3" s="27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
+      <c r="A4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="27" t="n">
+        <v>100001</v>
+      </c>
+      <c r="D4" s="27" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="8">
-      <c r="A5" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="17" t="n">
-        <v>1</v>
+      <c r="A5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>3</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="8">
-      <c r="A6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>2</v>
+      <c r="A6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>4</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="17" t="n">
-        <v>3</v>
+      <c r="A7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>5</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="18" t="n">
-        <v>4</v>
+      <c r="A8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>6</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="17" t="n">
-        <v>5</v>
+      <c r="A9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="23" t="n">
+        <v>7</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>6</v>
+      <c r="A10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>8</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>7</v>
+      <c r="A11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>9</v>
       </c>
       <c r="C11" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="18" t="n">
-        <v>8</v>
+      <c r="A12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>10</v>
       </c>
       <c r="C12" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>9</v>
+      <c r="A13" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>100001</v>
+        <v>100008</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="18" t="n">
-        <v>10</v>
+      <c r="A14" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>2</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>100001</v>
+        <v>100008</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n">
+      <c r="A15" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="17" t="n">
-        <v>1</v>
+      <c r="B15" s="23" t="n">
+        <v>3</v>
       </c>
       <c r="C15" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="n">
+      <c r="A16" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="18" t="n">
-        <v>2</v>
+      <c r="B16" s="24" t="n">
+        <v>4</v>
       </c>
       <c r="C16" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n">
+      <c r="A17" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="17" t="n">
-        <v>3</v>
+      <c r="B17" s="23" t="n">
+        <v>5</v>
       </c>
       <c r="C17" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="n">
+      <c r="A18" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="18" t="n">
-        <v>4</v>
+      <c r="B18" s="24" t="n">
+        <v>6</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n">
+      <c r="A19" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="17" t="n">
-        <v>5</v>
+      <c r="B19" s="23" t="n">
+        <v>7</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="n">
+      <c r="A20" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="18" t="n">
-        <v>6</v>
+      <c r="B20" s="24" t="n">
+        <v>8</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n">
+      <c r="A21" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="17" t="n">
-        <v>7</v>
+      <c r="B21" s="23" t="n">
+        <v>9</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n">
+      <c r="A22" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="18" t="n">
-        <v>8</v>
+      <c r="B22" s="24" t="n">
+        <v>10</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>9</v>
+      <c r="A23" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="18" t="n">
-        <v>10</v>
+      <c r="A24" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>100008</v>
+        <v>100009</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="0" t="n">
-        <v>100008</v>
-      </c>
+      <c r="A25" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="0" t="n"/>
       <c r="D25" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="0" t="n">
-        <v>100009</v>
-      </c>
-      <c r="D26" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>key:1</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>key:1</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="28" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B2">

--- a/resources/fabao.xlsx
+++ b/resources/fabao.xlsx
@@ -867,7 +867,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -932,24 +932,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1735,7 +1718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1833,17 +1816,17 @@
       <c r="A5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>无敌法宝</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Icon_fabao_01.png</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>这是一个神奇的法宝</t>
         </is>
@@ -1859,17 +1842,17 @@
       <c r="A6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>测试法宝2</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Icon_fabao_02.png</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>法宝的基础描述</t>
         </is>
@@ -1887,19 +1870,19 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" s="8">
       <c r="A7" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>测试法宝3</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Icon_fabao_03.png</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>测试描述修改</t>
         </is>
@@ -1912,10 +1895,29 @@
       <c r="F7" s="11" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="8">
-      <c r="B8" s="19" t="n"/>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="11" t="n"/>
+      <c r="A8" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>测试法宝4</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Icon_fabao_04.png</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>法宝的基础描述3</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>10009,1</t>
+        </is>
+      </c>
       <c r="F8" s="11" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="8">
@@ -1939,8 +1941,20 @@
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="11" t="n"/>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="8"/>
-    <row r="13" ht="16.5" customHeight="1" s="8"/>
+    <row r="12" ht="16.5" customHeight="1" s="8">
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="8">
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A9:A1048576">
     <cfRule type="duplicateValues" priority="11" dxfId="0"/>
@@ -2017,7 +2031,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>10070,5</t>
+          <t>15004,1</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
@@ -2065,59 +2079,68 @@
     </row>
     <row r="9" ht="16.5" customHeight="1" s="8">
       <c r="A9" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>15004,6</t>
+          <t>15004,5</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>15020,3</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="8">
       <c r="A10" s="16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>15004,7</t>
+          <t>15004,6</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="8">
       <c r="A11" s="16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>15004,8</t>
+          <t>15004,7</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="8">
       <c r="A12" s="16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>15004,9</t>
+          <t>15004,8</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="8">
       <c r="A13" s="16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>15004,10</t>
+          <t>15004,9</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="8">
       <c r="A14" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="11" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>15004,10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A15:A1048576">
@@ -2134,7 +2157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.5" customWidth="1" style="9" min="1" max="2"/>
@@ -2187,344 +2210,330 @@
       </c>
     </row>
     <row r="3" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="27" t="n">
-        <v>100001</v>
-      </c>
-      <c r="D3" s="27" t="n">
-        <v>1</v>
-      </c>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>key:1</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>key:1</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
     </row>
     <row r="4" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="27" t="n">
-        <v>100001</v>
-      </c>
-      <c r="D4" s="27" t="n">
-        <v>20</v>
-      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="8">
-      <c r="A5" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="23" t="n">
-        <v>3</v>
+      <c r="A5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="8">
-      <c r="A6" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="24" t="n">
-        <v>4</v>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="23" t="n">
-        <v>5</v>
+      <c r="A7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="24" t="n">
-        <v>6</v>
+      <c r="A8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="23" t="n">
-        <v>7</v>
+      <c r="A9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>5</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="24" t="n">
-        <v>8</v>
+      <c r="A10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="23" t="n">
-        <v>9</v>
+      <c r="A11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>7</v>
       </c>
       <c r="C11" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="24" t="n">
-        <v>10</v>
+      <c r="A12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="C12" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="D12" s="0" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="D14" s="0" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="23" t="n">
+    <row r="15">
+      <c r="A15" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>100008</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>100008</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="23" t="n">
-        <v>3</v>
+      <c r="B15" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="C15" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="24" t="n">
-        <v>4</v>
+      <c r="B16" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C16" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="23" t="n">
-        <v>5</v>
+      <c r="B17" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="C17" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="24" t="n">
-        <v>6</v>
+      <c r="B18" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="n">
+      <c r="A19" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="23" t="n">
-        <v>7</v>
+      <c r="B19" s="17" t="n">
+        <v>5</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="n">
+      <c r="A20" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="24" t="n">
-        <v>8</v>
+      <c r="B20" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="n">
+      <c r="A21" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="23" t="n">
-        <v>9</v>
+      <c r="B21" s="17" t="n">
+        <v>7</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="n">
+      <c r="A22" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="24" t="n">
-        <v>10</v>
+      <c r="B22" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="23" t="n">
-        <v>1</v>
+      <c r="A23" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>9</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>100008</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="n">
+      <c r="A24" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>100008</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>100008</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="0" t="n">
+      <c r="B26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="0" t="n">
         <v>100009</v>
       </c>
-      <c r="D24" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="0" t="n"/>
-      <c r="D25" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>key:1</t>
-        </is>
-      </c>
-      <c r="B26" s="28" t="inlineStr">
-        <is>
-          <t>key:1</t>
-        </is>
-      </c>
-      <c r="C26" s="28" t="n"/>
-      <c r="D26" s="28" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="n"/>
-      <c r="B27" s="23" t="n"/>
-      <c r="C27" s="28" t="n"/>
-      <c r="D27" s="28" t="n"/>
+      <c r="D26" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B2">

--- a/resources/fabao.xlsx
+++ b/resources/fabao.xlsx
@@ -1502,7 +1502,7 @@
           <t>生成文件</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SERVER</t>
         </is>
@@ -1520,7 +1520,7 @@
       <c r="E4" s="0" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
@@ -1537,7 +1537,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="0" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>SERVER</t>
         </is>
@@ -1554,7 +1554,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
@@ -1571,7 +1571,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>SERVER</t>
         </is>
@@ -1588,7 +1588,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="0" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
@@ -1605,7 +1605,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>SERVER</t>
         </is>
@@ -1622,7 +1622,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="0" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
@@ -1639,7 +1639,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="0" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>SERVER</t>
         </is>
@@ -1656,7 +1656,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="0" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
@@ -1673,12 +1673,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>SERVER</t>
         </is>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>FabaoQuality</t>
         </is>
@@ -1690,17 +1690,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="0" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>FabaoQuality</t>
         </is>
       </c>
-      <c r="D15" s="0" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>fabao/fabao_quality.py</t>
         </is>
